--- a/results/CB/Corrections_by_Cohort_Date_SessionType_Subject.xlsx
+++ b/results/CB/Corrections_by_Cohort_Date_SessionType_Subject.xlsx
@@ -462,112 +462,112 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45246</v>
+        <v>45216</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>apollo</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45246</v>
+        <v>45220</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>apollo</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45246</v>
+        <v>45207</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45246</v>
+        <v>45208</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45246</v>
+        <v>45209</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -577,43 +577,43 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45247</v>
+        <v>45219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45247</v>
+        <v>45220</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>ash</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -623,34 +623,34 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45247</v>
+        <v>45206</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45247</v>
+        <v>45207</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -659,145 +659,145 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45247</v>
+        <v>45210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>atom</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45248</v>
+        <v>45206</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>bonnie</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45248</v>
+        <v>45207</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>bonnie</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45248</v>
+        <v>45208</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>bonnie</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45249</v>
+        <v>45216</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>pumba</t>
+          <t>bonnie</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45249</v>
+        <v>45221</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>bonnie</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -811,20 +811,20 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45249</v>
+        <v>45246</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="18">
@@ -834,20 +834,20 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45249</v>
+        <v>45247</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -857,85 +857,85 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45250</v>
+        <v>45253</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CBR3</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>clover</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45250</v>
+        <v>45206</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>freya</t>
+          <t>dodge</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45250</v>
+        <v>45220</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>dodge</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45250</v>
+        <v>45221</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>dodge</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -945,70 +945,70 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45251</v>
+        <v>45208</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>george</t>
+          <t>dougie</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45251</v>
+        <v>45209</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>dougie</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45251</v>
+        <v>45219</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>dougie</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1018,20 +1018,20 @@
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45252</v>
+        <v>45246</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1041,20 +1041,20 @@
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45253</v>
+        <v>45247</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>clover</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="28">
@@ -1064,20 +1064,20 @@
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45253</v>
+        <v>45248</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -1087,20 +1087,20 @@
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45255</v>
+        <v>45249</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45256</v>
+        <v>45257</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>gio</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1133,7 +1133,7 @@
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45256</v>
+        <v>45258</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>nix</t>
+          <t>dusty</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1152,24 +1152,24 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CSU</t>
+          <t>HD</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45257</v>
+        <v>45207</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>filly</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33">
@@ -1179,20 +1179,20 @@
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45257</v>
+        <v>45250</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>myrtle</t>
+          <t>freya</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -1202,20 +1202,20 @@
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45257</v>
+        <v>45251</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>yoshi</t>
+          <t>george</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -1225,20 +1225,20 @@
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45257</v>
+        <v>45246</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>jelly</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -1248,20 +1248,20 @@
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45257</v>
+        <v>45247</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>smudge</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -1271,135 +1271,135 @@
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45258</v>
+        <v>45248</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>dusty</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45206</v>
+        <v>45249</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B39" s="2" t="n">
-        <v>45206</v>
+        <v>45251</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>bonnie</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B40" s="2" t="n">
-        <v>45206</v>
+        <v>45256</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>dodge</t>
+          <t>gio</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B41" s="2" t="n">
-        <v>45206</v>
+        <v>45250</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>molly</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B42" s="2" t="n">
-        <v>45206</v>
+        <v>45257</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CBF2</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>teddy</t>
+          <t>jelly</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -1409,16 +1409,16 @@
         </is>
       </c>
       <c r="B43" s="2" t="n">
-        <v>45207</v>
+        <v>45206</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>ash</t>
+          <t>molly</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -1436,16 +1436,16 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>bonnie</t>
+          <t>molly</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -1455,20 +1455,20 @@
         </is>
       </c>
       <c r="B45" s="2" t="n">
-        <v>45207</v>
+        <v>45210</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CBF3</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>mowgli</t>
+          <t>molly</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>teddy</t>
+          <t>mowgli</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -1501,154 +1501,154 @@
         </is>
       </c>
       <c r="B47" s="2" t="n">
-        <v>45207</v>
+        <v>45220</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>mowgli</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B48" s="2" t="n">
-        <v>45207</v>
+        <v>45246</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>filly</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B49" s="2" t="n">
-        <v>45207</v>
+        <v>45248</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>molly</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B50" s="2" t="n">
-        <v>45208</v>
+        <v>45249</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>bonnie</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B51" s="2" t="n">
-        <v>45208</v>
+        <v>45250</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>ash</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B52" s="2" t="n">
-        <v>45208</v>
+        <v>45257</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CBR2</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>dougie</t>
+          <t>myrtle</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B53" s="2" t="n">
-        <v>45209</v>
+        <v>45247</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR1</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ash</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -1658,103 +1658,103 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B54" s="2" t="n">
-        <v>45209</v>
+        <v>45251</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>dougie</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B55" s="2" t="n">
-        <v>45209</v>
+        <v>45255</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>teddy</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B56" s="2" t="n">
-        <v>45210</v>
+        <v>45256</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CBR1</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>molly</t>
+          <t>nix</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B57" s="2" t="n">
-        <v>45210</v>
+        <v>45249</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CBT1</t>
+          <t>CBR2</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>atom</t>
+          <t>pumba</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B58" s="2" t="n">
-        <v>45216</v>
+        <v>45252</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -1763,34 +1763,34 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B59" s="2" t="n">
-        <v>45216</v>
+        <v>45257</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBT4</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>bonnie</t>
+          <t>smudge</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="60">
@@ -1800,11 +1800,11 @@
         </is>
       </c>
       <c r="B60" s="2" t="n">
-        <v>45216</v>
+        <v>45206</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CBT2</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1823,20 +1823,20 @@
         </is>
       </c>
       <c r="B61" s="2" t="n">
-        <v>45219</v>
+        <v>45207</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>ash</t>
+          <t>teddy</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="62">
@@ -1846,16 +1846,16 @@
         </is>
       </c>
       <c r="B62" s="2" t="n">
-        <v>45219</v>
+        <v>45209</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>dougie</t>
+          <t>teddy</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -1869,16 +1869,16 @@
         </is>
       </c>
       <c r="B63" s="2" t="n">
-        <v>45220</v>
+        <v>45216</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>apollo</t>
+          <t>teddy</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -1888,89 +1888,89 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B64" s="2" t="n">
-        <v>45220</v>
+        <v>45246</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CBT3</t>
+          <t>CBF2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>dodge</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B65" s="2" t="n">
-        <v>45220</v>
+        <v>45247</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBF3</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>ash</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B66" s="2" t="n">
-        <v>45220</v>
+        <v>45250</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBR3</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>mowgli</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B67" s="2" t="n">
-        <v>45221</v>
+        <v>45253</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>bonnie</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E67" t="n">
@@ -1980,24 +1980,24 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>HD</t>
+          <t>CSU</t>
         </is>
       </c>
       <c r="B68" s="2" t="n">
-        <v>45221</v>
+        <v>45257</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CBT4</t>
+          <t>CBT3</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>dodge</t>
+          <t>yoshi</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/results/CB/Corrections_by_Cohort_Date_SessionType_Subject.xlsx
+++ b/results/CB/Corrections_by_Cohort_Date_SessionType_Subject.xlsx
@@ -1951,7 +1951,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="67">
